--- a/test/session--empty-statements/reference/2 semester 15 subjects/II семестр/25-5/Відомості 25-5.xlsx
+++ b/test/session--empty-statements/reference/2 semester 15 subjects/II семестр/25-5/Відомості 25-5.xlsx
@@ -27,7 +27,7 @@
     <definedName name="Ф80" localSheetId="3">#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Зведена J3'!$C$3:$T$23</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcMode="autoNoTable" fullCalcOnLoad="1"/>
+  <calcPr calcId="152511" calcMode="autoNoTable" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="F49" s="63">
-        <f>IF(F46="Очікую","Очікую",IF(F46-COUNTIF($U$10:$U40," - ")&lt;ROUNDDOWN(F46*0.4,0),F46-COUNTIF($U$10:$U40," - "),ROUNDDOWN(F46*0.4,0)))</f>
+        <f>IF(F46="Очікую","Очікую",IF(F46-COUNTIF($U$10:$U40," - ")&lt;ROUNDDOWN(F46*0.45,0),F46-COUNTIF($U$10:$U40," - "),ROUNDDOWN(F46*0.45,0)))</f>
         <v/>
       </c>
       <c r="G49" s="6" t="n"/>
@@ -3045,7 +3045,7 @@
       <c r="O49" s="6" t="n"/>
       <c r="P49" s="54" t="inlineStr">
         <is>
-          <t>Margarita BRITIKOVA</t>
+          <t>Маргарита БРІТІКОВА</t>
         </is>
       </c>
       <c r="Q49" s="54" t="n"/>
@@ -3339,7 +3339,7 @@
       <c r="B5" s="12" t="n"/>
       <c r="C5" s="73" t="inlineStr">
         <is>
-          <t>Успішності студентів спеціальності G13 ««Харчові технології»»</t>
+          <t>Успішності студентів спеціальності G13 «Харчові технології»</t>
         </is>
       </c>
       <c r="D5" s="92" t="n"/>
@@ -4990,7 +4990,7 @@
         </is>
       </c>
       <c r="F31" s="63">
-        <f>IF(F28="Очікую","Очікую",IF(F28-COUNTIF($U$10:$U22," - ")&lt;ROUNDDOWN(F28*0.4,0),F28-COUNTIF($U$10:$U22," - "),ROUNDDOWN(F28*0.4,0)))</f>
+        <f>IF(F28="Очікую","Очікую",IF(F28-COUNTIF($U$10:$U22," - ")&lt;ROUNDDOWN(F28*0.45,0),F28-COUNTIF($U$10:$U22," - "),ROUNDDOWN(F28*0.45,0)))</f>
         <v/>
       </c>
       <c r="G31" s="6" t="n"/>
@@ -5008,7 +5008,7 @@
       <c r="O31" s="6" t="n"/>
       <c r="P31" s="56" t="inlineStr">
         <is>
-          <t>Margarita BRITIKOVA</t>
+          <t>Маргарита БРІТІКОВА</t>
         </is>
       </c>
       <c r="Q31" s="54" t="n"/>
@@ -5324,7 +5324,7 @@
       <c r="B5" s="12" t="n"/>
       <c r="C5" s="73" t="inlineStr">
         <is>
-          <t>Успішності студентів спеціальності J2 ««Готельно-ресторанна справа та кейтеринг»»</t>
+          <t>Успішності студентів спеціальності J2 «Готельно-ресторанна справа та кейтеринг»</t>
         </is>
       </c>
       <c r="D5" s="92" t="n"/>
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="F31" s="63">
-        <f>IF(F28="Очікую","Очікую",IF(F28-COUNTIF($U$10:$U22," - ")&lt;ROUNDDOWN(F28*0.4,0),F28-COUNTIF($U$10:$U22," - "),ROUNDDOWN(F28*0.4,0)))</f>
+        <f>IF(F28="Очікую","Очікую",IF(F28-COUNTIF($U$10:$U22," - ")&lt;ROUNDDOWN(F28*0.45,0),F28-COUNTIF($U$10:$U22," - "),ROUNDDOWN(F28*0.45,0)))</f>
         <v/>
       </c>
       <c r="G31" s="6" t="n"/>
@@ -6993,7 +6993,7 @@
       <c r="O31" s="6" t="n"/>
       <c r="P31" s="56" t="inlineStr">
         <is>
-          <t>Margarita BRITIKOVA</t>
+          <t>Маргарита БРІТІКОВА</t>
         </is>
       </c>
       <c r="Q31" s="54" t="n"/>
@@ -7309,7 +7309,7 @@
       <c r="B5" s="12" t="n"/>
       <c r="C5" s="73" t="inlineStr">
         <is>
-          <t>Успішності студентів спеціальності J3 ««Туризм та рекреація»»</t>
+          <t>Успішності студентів спеціальності J3 «Туризм та рекреація»</t>
         </is>
       </c>
       <c r="D5" s="92" t="n"/>
@@ -8312,7 +8312,7 @@
         </is>
       </c>
       <c r="F23" s="63">
-        <f>IF(F20="Очікую","Очікую",IF(F20-COUNTIF($U$10:$U14," - ")&lt;ROUNDDOWN(F20*0.4,0),F20-COUNTIF($U$10:$U14," - "),ROUNDDOWN(F20*0.4,0)))</f>
+        <f>IF(F20="Очікую","Очікую",IF(F20-COUNTIF($U$10:$U14," - ")&lt;ROUNDDOWN(F20*0.45,0),F20-COUNTIF($U$10:$U14," - "),ROUNDDOWN(F20*0.45,0)))</f>
         <v/>
       </c>
       <c r="G23" s="6" t="n"/>
@@ -8330,7 +8330,7 @@
       <c r="O23" s="6" t="n"/>
       <c r="P23" s="56" t="inlineStr">
         <is>
-          <t>Margarita BRITIKOVA</t>
+          <t>Маргарита БРІТІКОВА</t>
         </is>
       </c>
       <c r="Q23" s="54" t="n"/>
